--- a/Reports/final_rankings.xlsx
+++ b/Reports/final_rankings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mohit Kumar</t>
+          <t xml:space="preserve">Mohit Kumar </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,7 +504,7 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>98.57142857142858</v>
+        <v>97.54098360655738</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shivangi Pandey</t>
+          <t>Vibhu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>shivangipandeyabc@gmail.com</t>
+          <t>vibhubtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95.58823529411765</v>
+        <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>97.14285714285714</v>
+        <v>97.54098360655738</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -544,23 +544,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chetan gooswami</t>
+          <t xml:space="preserve">Shivangi Pandey </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chetangoswami2006@gmail.com</t>
+          <t>shivangipandeyabc@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>93.75</v>
+        <v>95.58823529411765</v>
       </c>
       <c r="E5" t="n">
-        <v>95.71428571428572</v>
+        <v>95.08196721311475</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
         <v>93.44262295081968</v>
       </c>
       <c r="E6" t="n">
-        <v>94.28571428571428</v>
+        <v>93.44262295081968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amrendra Ram Tripathi</t>
+          <t xml:space="preserve">Amrendra Ram Tripathi </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,7 +608,7 @@
         <v>93.33333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>92.85714285714286</v>
+        <v>91.80327868852459</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -627,14 +627,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chetangoswamibtech23-27@liet.in</t>
+          <t>chetangoswami2006@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93.04347826086956</v>
+        <v>93.12977099236642</v>
       </c>
       <c r="E8" t="n">
-        <v>91.42857142857143</v>
+        <v>90.1639344262295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -648,15 +648,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t xml:space="preserve">Ansh Tyagi </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>anshtyagi189@gmail.com</t>
+        </is>
+      </c>
       <c r="D9" t="n">
-        <v>92.6829268292683</v>
+        <v>92.19858156028369</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>88.52459016393442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -670,19 +674,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ansh Tyagi</t>
+          <t>Ritesh Kumar Singh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>anshtyagi189@gmail.com</t>
+          <t>riteshkumar07.com@gmail.com</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>92.19858156028369</v>
+        <v>92.10526315789474</v>
       </c>
       <c r="E10" t="n">
-        <v>88.57142857142857</v>
+        <v>86.88524590163934</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -696,19 +700,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ritesh Kumar Singh</t>
+          <t xml:space="preserve">Kanak Gupta </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>riteshkumar07.com@gmail.com</t>
+          <t>kanak.gup1234@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>92.10526315789474</v>
+        <v>91.30434782608695</v>
       </c>
       <c r="E11" t="n">
-        <v>87.14285714285714</v>
+        <v>85.24590163934425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -722,19 +726,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kanak Gupta</t>
+          <t>Anurag Kumar Singh</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kanak.gup1234@gmail.com</t>
+          <t>anusingh99361634@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>91.30434782608695</v>
+        <v>91</v>
       </c>
       <c r="E12" t="n">
-        <v>85.71428571428571</v>
+        <v>83.60655737704919</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -748,19 +752,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anurag Kumar Singh</t>
+          <t xml:space="preserve">Harshit Rai </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>anusingh99361634@gmail.com</t>
+          <t>harshitraibtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>91</v>
+        <v>90.83969465648855</v>
       </c>
       <c r="E13" t="n">
-        <v>84.28571428571429</v>
+        <v>81.9672131147541</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -774,19 +778,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Harshit Rai</t>
+          <t xml:space="preserve">Nilesh Sarkar </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>harshitrai1822@gmail.com</t>
+          <t>nileshsarkar430@email.com</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90.83969465648855</v>
+        <v>90</v>
       </c>
       <c r="E14" t="n">
-        <v>82.85714285714286</v>
+        <v>79.50819672131148</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -796,23 +800,23 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gunjan </t>
+          <t>Lalit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gunjanchaudhary@liet.in</t>
+          <t>23lalitthakur@gmail.com</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90.2439024390244</v>
+        <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>81.42857142857143</v>
+        <v>79.50819672131148</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -826,23 +830,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lalit</t>
+          <t>Prem Kumar Jha</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23lalitthakur@gmail.com</t>
+          <t>premkumarjhabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>89.65517241379311</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>77.04918032786885</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -852,19 +856,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prem Kumar Jha</t>
+          <t xml:space="preserve">Gunjan </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>premkumarjhabtech23-27@liet.in</t>
+          <t>gunjanbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>89.65517241379311</v>
+        <v>89.31297709923665</v>
       </c>
       <c r="E17" t="n">
-        <v>78.57142857142857</v>
+        <v>75.40983606557377</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -878,19 +882,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gunjan</t>
+          <t xml:space="preserve">Vipul Pandey </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>gunjanbtech23-27@liet.in</t>
+          <t>vipulpandeybtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>88.88888888888889</v>
+        <v>88.35616438356165</v>
       </c>
       <c r="E18" t="n">
-        <v>77.14285714285715</v>
+        <v>73.77049180327869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -904,19 +908,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vipul Pandey</t>
+          <t>Anushka Garg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>vipulpandeybtech23-27@liet.in</t>
+          <t>anushkagargbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>88.35616438356165</v>
+        <v>88.1578947368421</v>
       </c>
       <c r="E19" t="n">
-        <v>75.71428571428571</v>
+        <v>72.1311475409836</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -930,19 +934,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anushka Garg</t>
+          <t xml:space="preserve">Aman Singh </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>anushkagargbtech23-27@liet.in</t>
+          <t>amans64788@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>88.1578947368421</v>
+        <v>87.5</v>
       </c>
       <c r="E20" t="n">
-        <v>74.28571428571429</v>
+        <v>70.49180327868852</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -956,15 +960,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t xml:space="preserve">Prateek Rai </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>prateekraibtech23-27@liet.in</t>
+        </is>
+      </c>
       <c r="D21" t="n">
-        <v>87.80487804878049</v>
+        <v>86.76470588235294</v>
       </c>
       <c r="E21" t="n">
-        <v>72.85714285714285</v>
+        <v>68.85245901639344</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -978,19 +986,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aman Singh</t>
+          <t>Sakshi Chauhan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>amans64788@gmail.com</t>
+          <t>sakshichauhanbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>87.5</v>
+        <v>83.85093167701864</v>
       </c>
       <c r="E22" t="n">
-        <v>71.42857142857143</v>
+        <v>67.21311475409836</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1004,19 +1012,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prateek Rai</t>
+          <t>Rahul Yadav</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>raiprateek009@gmail.com</t>
+          <t>rahulyadavbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>86.76470588235294</v>
+        <v>83.01886792452831</v>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>65.57377049180327</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1030,19 +1038,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sakshi Chauhan</t>
+          <t>MOHIT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sakshichauhan5997@gmail.com</t>
+          <t>mohitbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>83.85093167701864</v>
+        <v>82.78145695364239</v>
       </c>
       <c r="E24" t="n">
-        <v>68.57142857142857</v>
+        <v>63.9344262295082</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1056,19 +1064,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rahul Yadav</t>
+          <t>Akash Kumar Yadav</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rahulyadavbtech23-27@liet.in</t>
+          <t>akyadav5769@gmail.com</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>83.01886792452831</v>
+        <v>82.22222222222221</v>
       </c>
       <c r="E25" t="n">
-        <v>67.14285714285714</v>
+        <v>62.29508196721311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1082,19 +1090,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mohit</t>
+          <t>Tarun kumar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mohitbtech23-27@liet.in</t>
+          <t>tarunkumar1btech23-27@liet.in</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>82.78145695364239</v>
+        <v>80.15267175572519</v>
       </c>
       <c r="E26" t="n">
-        <v>65.71428571428571</v>
+        <v>60.65573770491803</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1108,19 +1116,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Akash Kumar Yadav</t>
+          <t>Vineet Kumar Roy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>akyadav5769@gmail.com</t>
+          <t>vineet333roy@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>82.22222222222221</v>
+        <v>80</v>
       </c>
       <c r="E27" t="n">
-        <v>64.28571428571429</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1130,23 +1138,23 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mushroop</t>
+          <t>Garima Singh</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mushroopmd08@gmail.com</t>
+          <t>gsinghakca@gmail.com</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>81.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="E28" t="n">
-        <v>62.14285714285715</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1156,23 +1164,23 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jai Vardhan Singh</t>
+          <t xml:space="preserve">Nikhil Sharma </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jaivardhansinghbtech23-27@liet.in</t>
+          <t>nikhilsharmabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>81.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>62.14285714285715</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1186,23 +1194,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tarun Kumar</t>
+          <t>Aman singh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>tarunpandit885@gmail.com</t>
+          <t>amansingh1btech23-27@liet.in</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80.15267175572519</v>
+        <v>79.43262411347519</v>
       </c>
       <c r="E30" t="n">
-        <v>60</v>
+        <v>54.09836065573771</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
@@ -1212,75 +1220,75 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nikhil Sharma</t>
+          <t xml:space="preserve">Shivam Chaudhary </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ns977440@gmail.com</t>
+          <t>shivamchaudharybtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>79.36507936507937</v>
       </c>
       <c r="E31" t="n">
-        <v>57.14285714285714</v>
+        <v>52.45901639344262</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Garima Singh</t>
+          <t>Ayush Pal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gsinghakca@gmail.com</t>
+          <t>ayushpalbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>80</v>
+        <v>78.44827586206897</v>
       </c>
       <c r="E32" t="n">
-        <v>57.14285714285714</v>
+        <v>50.81967213114754</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vineet Kumar Roy</t>
+          <t>Anshu Gupta</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>vineet333roy@gmail.com</t>
+          <t>ansh.gup067@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>80</v>
+        <v>78.21782178217822</v>
       </c>
       <c r="E33" t="n">
-        <v>57.14285714285714</v>
+        <v>49.18032786885246</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
@@ -1290,19 +1298,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nilesh Sarkar</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nileshsarkar430@gmail.com</t>
+          <t>happybtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>79.50310559006211</v>
+        <v>78.08219178082192</v>
       </c>
       <c r="E34" t="n">
-        <v>54.28571428571428</v>
+        <v>47.54098360655738</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1316,19 +1324,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aman Singh</t>
+          <t xml:space="preserve">Nilesh Sarkar </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>amansingh1btech23-27@liet.in</t>
+          <t>nileshsarkar430@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>79.43262411347519</v>
+        <v>78.01418439716312</v>
       </c>
       <c r="E35" t="n">
-        <v>52.85714285714286</v>
+        <v>45.90163934426229</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1342,19 +1350,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shivam Chaudhary</t>
+          <t xml:space="preserve">Satyansh Rawat </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>shivamchaudharybtech23-27@liet.in</t>
+          <t>satyanshrawatbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>79.36507936507937</v>
+        <v>77.86259541984732</v>
       </c>
       <c r="E36" t="n">
-        <v>51.42857142857142</v>
+        <v>44.26229508196721</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1368,19 +1376,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vishujeet Rathore</t>
+          <t>Jai Vardhan Singh</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>vishujeetrathor@gmail.com</t>
+          <t>jaisingh1256301@gmail.com</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>79.33884297520662</v>
+        <v>77.63157894736842</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>42.62295081967213</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1394,19 +1402,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ayush Pal</t>
+          <t>Vivek Yadav</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ayushpalbtech23-27@liet.in</t>
+          <t>vivekyadavbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>78.44827586206897</v>
+        <v>77.01863354037268</v>
       </c>
       <c r="E38" t="n">
-        <v>48.57142857142857</v>
+        <v>40.98360655737705</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1420,19 +1428,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Anshu Gupta</t>
+          <t>Devashish Dobhal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ansh.gup067@gmail.com</t>
+          <t>devashishdobhalbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>78.21782178217822</v>
+        <v>76.82119205298014</v>
       </c>
       <c r="E39" t="n">
-        <v>47.14285714285714</v>
+        <v>39.34426229508197</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1446,19 +1454,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Ayush Saw</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>happybtech23-27@liet.in</t>
+          <t>ayushsawbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>78.08219178082192</v>
+        <v>76.74418604651163</v>
       </c>
       <c r="E40" t="n">
-        <v>45.71428571428572</v>
+        <v>37.70491803278689</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1472,19 +1480,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Satyansh Rawat</t>
+          <t xml:space="preserve">Mushroop </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>satyanshrawatbtech23-27@liet.in</t>
+          <t>mushroopbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>77.86259541984732</v>
+        <v>76.33587786259542</v>
       </c>
       <c r="E41" t="n">
-        <v>44.28571428571428</v>
+        <v>36.0655737704918</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1498,19 +1506,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vivek Yadav</t>
+          <t xml:space="preserve">Sringani Singh </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>vivekyadavbtech23-27@liet.in</t>
+          <t>sringanisinghbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.01863354037268</v>
+        <v>75.65217391304347</v>
       </c>
       <c r="E42" t="n">
-        <v>42.85714285714285</v>
+        <v>34.42622950819672</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1524,19 +1532,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Devashish Dobhal</t>
+          <t>Kapil Yadav</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>devashishdobhalbtech23-27@liet.in</t>
+          <t>ky205426@gmail.com</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>76.82119205298014</v>
+        <v>74.04580152671755</v>
       </c>
       <c r="E43" t="n">
-        <v>41.42857142857143</v>
+        <v>32.78688524590164</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1550,19 +1558,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ayush Saw</t>
+          <t xml:space="preserve">Nisha Gupta </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ayushsawbtech23-27@liet.in</t>
+          <t>nishaguptabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>76.74418604651163</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="E44" t="n">
-        <v>40</v>
+        <v>31.14754098360656</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1576,19 +1584,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sringani Singh</t>
+          <t xml:space="preserve">Vishujeet Rathore </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sringanisinghbtech23-27@liet.in</t>
+          <t>vishujeetrathor@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>75.65217391304347</v>
+        <v>73.28767123287672</v>
       </c>
       <c r="E45" t="n">
-        <v>38.57142857142858</v>
+        <v>29.50819672131147</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1602,19 +1610,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mushroop </t>
+          <t xml:space="preserve">Gurmeet Singh </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mushroopbtech23-27@liet.in</t>
+          <t>gurmeetsinghbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>75</v>
+        <v>70.29702970297029</v>
       </c>
       <c r="E46" t="n">
-        <v>37.14285714285715</v>
+        <v>27.86885245901639</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1628,23 +1636,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kapil Yadav</t>
+          <t>Yash Bansal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ky205426@gmail.com</t>
+          <t>yashbansal216@gmail.com</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>74.04580152671755</v>
+        <v>69.41176470588235</v>
       </c>
       <c r="E47" t="n">
-        <v>35.71428571428572</v>
+        <v>26.22950819672131</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1654,23 +1662,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nisha Gupta</t>
+          <t>Ritik</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nishaguptabtech23-27@liet.in</t>
+          <t>kumarritik38269@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>73.33333333333333</v>
+        <v>68.94409937888199</v>
       </c>
       <c r="E48" t="n">
-        <v>34.28571428571428</v>
+        <v>24.59016393442623</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1680,19 +1688,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Yash Bansal</t>
+          <t>PIYUSH SINGH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>yashbansal216@gmail.com</t>
+          <t>piyushsingh1982004@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>69.41176470588235</v>
+        <v>68.49315068493151</v>
       </c>
       <c r="E49" t="n">
-        <v>32.85714285714285</v>
+        <v>22.95081967213115</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1706,19 +1714,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ritik</t>
+          <t>Vishal Kumar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kumarritik38269@gmail.com</t>
+          <t>vk9491015@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>68.94409937888199</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="E50" t="n">
-        <v>31.42857142857143</v>
+        <v>21.31147540983606</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1732,19 +1740,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>mushroop</t>
+          <t xml:space="preserve">Pushpendra Yadav </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mdmushroop@gmail.com</t>
+          <t>pushpendrayadav8434@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>68.57142857142857</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>19.67213114754098</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1758,19 +1766,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Piyush Singh</t>
+          <t>Vaibhav Mishra</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>piyushsinghbtech23-27@liet.in</t>
+          <t>vaibhavmishrabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>68.49315068493151</v>
+        <v>66</v>
       </c>
       <c r="E52" t="n">
-        <v>28.57142857142857</v>
+        <v>18.0327868852459</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1784,19 +1792,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vishal Kumar</t>
+          <t xml:space="preserve">Sanskar </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>vk9491015@gmail.com</t>
+          <t>sanskarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>67.64705882352942</v>
+        <v>62.66666666666667</v>
       </c>
       <c r="E53" t="n">
-        <v>27.14285714285714</v>
+        <v>16.39344262295082</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1810,19 +1818,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gurmeet Singh</t>
+          <t xml:space="preserve">Manish Mishra </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>gurmeetsinghbtech23-27@liet.in</t>
+          <t>manishjitendramishrabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>67.05882352941175</v>
+        <v>60</v>
       </c>
       <c r="E54" t="n">
-        <v>25.71428571428571</v>
+        <v>13.9344262295082</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1832,23 +1840,23 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pushpendra Yadav</t>
+          <t xml:space="preserve">Aman Kumar </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>pushpendrayadav8434@gmail.com</t>
+          <t>amankumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>66.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>24.28571428571428</v>
+        <v>13.9344262295082</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1862,23 +1870,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vaibhav Mishra</t>
+          <t xml:space="preserve">Shreyanshi Yadav </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>vaibhavmishrabtech23-27@liet.in</t>
+          <t>yadavshreyanshi772@gmail.com</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>66</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="E56" t="n">
-        <v>22.85714285714286</v>
+        <v>11.47540983606557</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1888,23 +1896,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sanskar</t>
+          <t xml:space="preserve">Rohit Kumar </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>solankisanskar01@gmail.com</t>
+          <t>rohitkumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>62.66666666666667</v>
+        <v>56.48854961832062</v>
       </c>
       <c r="E57" t="n">
-        <v>21.42857142857143</v>
+        <v>9.836065573770492</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1914,23 +1922,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jai</t>
+          <t>Sonu Kumar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jaisingh1256301@gmail.com</t>
+          <t>sonukumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>62.5</v>
+        <v>48.35164835164835</v>
       </c>
       <c r="E58" t="n">
-        <v>20</v>
+        <v>8.196721311475409</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -1940,19 +1948,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t xml:space="preserve">Krishna Kumar Sah </t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ksah9189@gmail.com</t>
+        </is>
+      </c>
       <c r="D59" t="n">
-        <v>60.97560975609756</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="E59" t="n">
-        <v>18.57142857142857</v>
+        <v>6.557377049180328</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -1962,23 +1974,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manish Mishra </t>
+          <t>Akeel khan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>manishjitendramishrabtech23-27@liet.in</t>
+          <t>mohammadakeelbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E60" t="n">
-        <v>17.14285714285714</v>
+        <v>4.918032786885246</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -1988,23 +2000,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shreyanshi Yadav</t>
+          <t>Akeel Khan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yadavshreyanshi022@gmail.com</t>
+          <t>akeelkhan3499@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>58.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="E61" t="n">
-        <v>15.71428571428571</v>
+        <v>3.278688524590164</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -2014,251 +2026,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rohit Kumar</t>
+          <t>Alok</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>rohitkumarbtech23-27@liet.in</t>
+          <t>alok_kumar@liet.in</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>56.48854961832062</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="E62" t="n">
-        <v>14.28571428571428</v>
+        <v>1.639344262295082</v>
       </c>
       <c r="F62" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="n">
-        <v>56.09756097560976</v>
-      </c>
-      <c r="E63" t="n">
-        <v>12.85714285714286</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Aman Kumar</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>amankumarbtech23-27@liet.in</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="E64" t="n">
-        <v>11.42857142857143</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Sonu Kumar</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>sonukumar3570357@gmail.com</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>48.35164835164835</v>
-      </c>
-      <c r="E65" t="n">
-        <v>10</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Krishna Kumar Sah</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>krishnakumarsahbtech23-27@liet.in</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>46.42857142857143</v>
-      </c>
-      <c r="E66" t="n">
-        <v>8.571428571428571</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Akeel khan</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>mohammadakeelbtech23-27@liet.in</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>35</v>
-      </c>
-      <c r="E67" t="n">
-        <v>7.142857142857142</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Aman Kumar</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ak8102347910@gmail.com</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="E68" t="n">
-        <v>5.714285714285714</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Jagat Kumar</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>jagat.kumar@liet.in</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="E69" t="n">
-        <v>4.285714285714286</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Mohammad Akeel</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>akeelkhan3499@gmail.com</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>25</v>
-      </c>
-      <c r="E70" t="n">
-        <v>2.857142857142857</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALOK </t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>alok_kumar@liet.in</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="F71" t="inlineStr">
         <is>
           <t>D</t>
         </is>
